--- a/examples/SESdummyData.xlsx
+++ b/examples/SESdummyData.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c1c5ca7ba7fc34b/WORK/GitHub/SES-hospedajes-assistant/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{53B68867-398C-400B-9C0F-5E21E308F144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{386C61DD-45B3-425A-9C82-D6F3515F949A}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{53B68867-398C-400B-9C0F-5E21E308F144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005D1A44-8543-43C1-A705-DF0B35C218F4}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="1740" windowWidth="21600" windowHeight="7170" xr2:uid="{25E99CB9-B179-4110-B74F-42B4546C7EC3}"/>
+    <workbookView xWindow="22740" yWindow="4035" windowWidth="23970" windowHeight="15615" xr2:uid="{25E99CB9-B179-4110-B74F-42B4546C7EC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Guests" sheetId="1" r:id="rId1"/>
+    <sheet name="orig" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Guests!$L$5:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">orig!$M$5:$M$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="88">
   <si>
     <t>Valid until…</t>
   </si>
@@ -234,6 +236,78 @@
   </si>
   <si>
     <t>reservation_number</t>
+  </si>
+  <si>
+    <t>nacionalidad</t>
+  </si>
+  <si>
+    <t>FechaNacimiento</t>
+  </si>
+  <si>
+    <t>numeroDocumento</t>
+  </si>
+  <si>
+    <t>tipoDocumento</t>
+  </si>
+  <si>
+    <t>apellido2</t>
+  </si>
+  <si>
+    <t>apellido1</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>FechaSalida</t>
+  </si>
+  <si>
+    <t>FechaEntrada</t>
+  </si>
+  <si>
+    <t>referencia</t>
+  </si>
+  <si>
+    <t>pago</t>
+  </si>
+  <si>
+    <t>persona</t>
+  </si>
+  <si>
+    <t>rol</t>
+  </si>
+  <si>
+    <t>security_code</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>municipalCode</t>
+  </si>
+  <si>
+    <t>municipalityName</t>
+  </si>
+  <si>
+    <t>postCode</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>relationship</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>placeOfBirth</t>
   </si>
 </sst>
 </file>
@@ -274,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +379,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -319,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -375,6 +461,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -391,6 +479,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -814,7 +906,7 @@
         <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -826,34 +918,34 @@
         <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1104,4 +1196,410 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE82CE7-7399-493F-9B35-2331F739D7A0}">
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="2" customWidth="1"/>
+    <col min="13" max="13" width="53.140625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="31.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19" style="14"/>
+    <col min="17" max="17" width="29" style="2" customWidth="1"/>
+    <col min="18" max="18" width="25" style="2" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="18"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="14"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>123456</v>
+      </c>
+      <c r="C2" s="7">
+        <v>13579</v>
+      </c>
+      <c r="D2" s="12">
+        <v>46144</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="20">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="19">
+        <v>209640</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="5" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="17">
+        <v>49834</v>
+      </c>
+      <c r="J6" s="17">
+        <v>32475</v>
+      </c>
+      <c r="K6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="7">
+        <v>661644154</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" s="2">
+        <v>41075</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T6" s="2">
+        <v>41840</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="17">
+        <v>47266</v>
+      </c>
+      <c r="J7" s="17">
+        <v>35831</v>
+      </c>
+      <c r="K7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="7">
+        <v>651131948</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="2">
+        <v>18111</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" s="2">
+        <v>18213</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="17">
+        <v>47437</v>
+      </c>
+      <c r="J8" s="17">
+        <v>35910</v>
+      </c>
+      <c r="K8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="7">
+        <v>661088226</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="2">
+        <v>20069</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" s="2">
+        <v>20014</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="S9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="L10" s="2"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="14"/>
+      <c r="S10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="10"/>
+      <c r="L11" s="2"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="14"/>
+    </row>
+    <row r="12" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="L12" s="2"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="L13" s="2"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="14"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O6" r:id="rId1" xr:uid="{E094CEC2-76A9-4E80-86BE-D98C49F1EE47}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/examples/SESdummyData.xlsx
+++ b/examples/SESdummyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c1c5ca7ba7fc34b/WORK/GitHub/SES-hospedajes-assistant/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{53B68867-398C-400B-9C0F-5E21E308F144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005D1A44-8543-43C1-A705-DF0B35C218F4}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{53B68867-398C-400B-9C0F-5E21E308F144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3519EC-4086-4DE2-97DB-DDE4A0A88A01}"/>
   <bookViews>
-    <workbookView xWindow="22740" yWindow="4035" windowWidth="23970" windowHeight="15615" xr2:uid="{25E99CB9-B179-4110-B74F-42B4546C7EC3}"/>
+    <workbookView xWindow="22740" yWindow="4035" windowWidth="23970" windowHeight="8610" xr2:uid="{25E99CB9-B179-4110-B74F-42B4546C7EC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Guests" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="89">
   <si>
     <t>Valid until…</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>placeOfBirth</t>
+  </si>
+  <si>
+    <t>ççç</t>
   </si>
 </sst>
 </file>
@@ -802,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF881FB-F0DD-4107-A574-EB5CEAF3F194}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="19" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -826,7 +829,7 @@
     <col min="20" max="20" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>23</v>
       </c>
@@ -858,7 +861,7 @@
       <c r="R1" s="11"/>
       <c r="S1" s="14"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -889,7 +892,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="5" spans="1:19" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
@@ -947,8 +950,11 @@
       <c r="S5" s="13" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>38</v>
       </c>
@@ -1007,7 +1013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>39</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
@@ -1125,12 +1131,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="N9" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="9"/>
@@ -1143,7 +1149,7 @@
       <c r="R10" s="11"/>
       <c r="S10" s="14"/>
     </row>
-    <row r="11" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="9"/>
@@ -1154,7 +1160,7 @@
       <c r="R11" s="11"/>
       <c r="S11" s="14"/>
     </row>
-    <row r="12" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="9"/>
@@ -1165,7 +1171,7 @@
       <c r="R12" s="11"/>
       <c r="S12" s="14"/>
     </row>
-    <row r="13" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="9"/>
@@ -1176,7 +1182,7 @@
       <c r="R13" s="11"/>
       <c r="S13" s="14"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
